--- a/mali.xlsx
+++ b/mali.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="19308" windowHeight="9588"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3464" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="746">
   <si>
     <t>Lieu</t>
   </si>
@@ -2249,76 +2265,913 @@
   </si>
   <si>
     <t>1 505</t>
-  </si>
-  <si>
-    <t>10 880</t>
-  </si>
-  <si>
-    <t>31 332</t>
-  </si>
-  <si>
-    <t>55 605</t>
-  </si>
-  <si>
-    <t>98 903</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2508,17 +3361,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:T227"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2538,7 +3393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:20">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2600,7 +3455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customHeight="1" spans="1:20">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -2614,7 +3469,7 @@
         <v>28</v>
       </c>
       <c r="E3" s="1">
-        <v>387416.0</v>
+        <v>387416</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
@@ -2659,7 +3514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customHeight="1" spans="1:20">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -2673,7 +3528,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>36</v>
@@ -2718,7 +3573,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:20">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -2732,7 +3587,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>37</v>
@@ -2777,7 +3632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customHeight="1" spans="1:20">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,7 +3646,7 @@
         <v>28</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -2836,7 +3691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customHeight="1" spans="1:20">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -2850,7 +3705,7 @@
         <v>40</v>
       </c>
       <c r="E7" s="1">
-        <v>350970.0</v>
+        <v>350970</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>29</v>
@@ -2895,7 +3750,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customHeight="1" spans="1:20">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -2909,7 +3764,7 @@
         <v>40</v>
       </c>
       <c r="E8" s="1">
-        <v>174.0</v>
+        <v>174</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>36</v>
@@ -2921,25 +3776,25 @@
         <v>32</v>
       </c>
       <c r="J8" s="1">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="K8" s="1">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="L8" s="1">
-        <v>139.0</v>
+        <v>139</v>
       </c>
       <c r="M8" s="1">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O8" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="P8" s="1">
-        <v>139.0</v>
+        <v>139</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>32</v>
@@ -2948,13 +3803,13 @@
         <v>32</v>
       </c>
       <c r="S8" s="1">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="T8" s="1">
-        <v>148.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:20">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2968,7 +3823,7 @@
         <v>40</v>
       </c>
       <c r="E9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>37</v>
@@ -3013,7 +3868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customHeight="1" spans="1:20">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -3027,7 +3882,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -3072,7 +3927,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customHeight="1" spans="1:20">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -3086,7 +3941,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="1">
-        <v>850903.0</v>
+        <v>850903</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>29</v>
@@ -3131,7 +3986,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customHeight="1" spans="1:20">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -3145,7 +4000,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>36</v>
@@ -3190,7 +4045,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:20">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -3204,7 +4059,7 @@
         <v>49</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>37</v>
@@ -3249,7 +4104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:20">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,7 +4118,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -3308,7 +4163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:20">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -3322,7 +4177,7 @@
         <v>56</v>
       </c>
       <c r="E15" s="1">
-        <v>326733.0</v>
+        <v>326733</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>29</v>
@@ -3367,7 +4222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customHeight="1" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -3381,7 +4236,7 @@
         <v>56</v>
       </c>
       <c r="E16" s="1">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>36</v>
@@ -3426,7 +4281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customHeight="1" spans="1:20">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -3440,7 +4295,7 @@
         <v>56</v>
       </c>
       <c r="E17" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>37</v>
@@ -3485,7 +4340,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customHeight="1" spans="1:20">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -3499,7 +4354,7 @@
         <v>56</v>
       </c>
       <c r="E18" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -3544,7 +4399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customHeight="1" spans="1:20">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -3558,7 +4413,7 @@
         <v>63</v>
       </c>
       <c r="E19" s="1">
-        <v>176418.0</v>
+        <v>176418</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>29</v>
@@ -3603,7 +4458,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customHeight="1" spans="1:20">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -3617,7 +4472,7 @@
         <v>63</v>
       </c>
       <c r="E20" s="1">
-        <v>917.0</v>
+        <v>917</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>36</v>
@@ -3662,7 +4517,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customHeight="1" spans="1:20">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -3676,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="E21" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>37</v>
@@ -3721,7 +4576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="1:20">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -3735,7 +4590,7 @@
         <v>63</v>
       </c>
       <c r="E22" s="1">
-        <v>1706.0</v>
+        <v>1706</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -3780,7 +4635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:20">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -3794,7 +4649,7 @@
         <v>69</v>
       </c>
       <c r="E23" s="1">
-        <v>379588.0</v>
+        <v>379588</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>29</v>
@@ -3839,7 +4694,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="1:20">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -3853,7 +4708,7 @@
         <v>69</v>
       </c>
       <c r="E24" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>36</v>
@@ -3898,7 +4753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customHeight="1" spans="1:20">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -3912,7 +4767,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>37</v>
@@ -3957,7 +4812,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customHeight="1" spans="1:20">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -3971,7 +4826,7 @@
         <v>69</v>
       </c>
       <c r="E26" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>38</v>
@@ -4016,7 +4871,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customHeight="1" spans="1:20">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -4030,7 +4885,7 @@
         <v>79</v>
       </c>
       <c r="E27" s="1">
-        <v>292687.0</v>
+        <v>292687</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>29</v>
@@ -4075,7 +4930,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customHeight="1" spans="1:20">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
@@ -4089,7 +4944,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>36</v>
@@ -4134,7 +4989,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customHeight="1" spans="1:20">
       <c r="A29" s="1" t="s">
         <v>25</v>
       </c>
@@ -4148,7 +5003,7 @@
         <v>79</v>
       </c>
       <c r="E29" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>37</v>
@@ -4193,7 +5048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" customHeight="1" spans="1:20">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -4207,7 +5062,7 @@
         <v>79</v>
       </c>
       <c r="E30" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -4252,7 +5107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" customHeight="1" spans="1:20">
       <c r="A31" s="1" t="s">
         <v>87</v>
       </c>
@@ -4266,7 +5121,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1">
-        <v>385896.0</v>
+        <v>385896</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>29</v>
@@ -4311,7 +5166,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customHeight="1" spans="1:20">
       <c r="A32" s="1" t="s">
         <v>87</v>
       </c>
@@ -4325,7 +5180,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>36</v>
@@ -4370,7 +5225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" customHeight="1" spans="1:20">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
@@ -4384,7 +5239,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>37</v>
@@ -4429,7 +5284,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" customHeight="1" spans="1:20">
       <c r="A34" s="1" t="s">
         <v>87</v>
       </c>
@@ -4443,7 +5298,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>38</v>
@@ -4488,7 +5343,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customHeight="1" spans="1:20">
       <c r="A35" s="1" t="s">
         <v>87</v>
       </c>
@@ -4502,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="1">
-        <v>9105.0</v>
+        <v>9105</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>29</v>
@@ -4529,10 +5384,10 @@
         <v>32</v>
       </c>
       <c r="O35" s="1">
-        <v>527.0</v>
+        <v>527</v>
       </c>
       <c r="P35" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>105</v>
@@ -4547,7 +5402,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" customHeight="1" spans="1:20">
       <c r="A36" s="1" t="s">
         <v>87</v>
       </c>
@@ -4561,13 +5416,13 @@
         <v>100</v>
       </c>
       <c r="E36" s="1">
-        <v>1821.0</v>
+        <v>1821</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H36" s="1">
-        <v>573.0</v>
+        <v>573</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>32</v>
@@ -4588,7 +5443,7 @@
         <v>32</v>
       </c>
       <c r="O36" s="1">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>108</v>
@@ -4606,7 +5461,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" customHeight="1" spans="1:20">
       <c r="A37" s="1" t="s">
         <v>87</v>
       </c>
@@ -4620,7 +5475,7 @@
         <v>100</v>
       </c>
       <c r="E37" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>37</v>
@@ -4635,22 +5490,22 @@
         <v>32</v>
       </c>
       <c r="K37" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="M37" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O37" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P37" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="1" t="s">
         <v>32</v>
@@ -4659,13 +5514,13 @@
         <v>32</v>
       </c>
       <c r="S37" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="T37" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:20">
       <c r="A38" s="1" t="s">
         <v>87</v>
       </c>
@@ -4679,7 +5534,7 @@
         <v>100</v>
       </c>
       <c r="E38" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>38</v>
@@ -4724,7 +5579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" customHeight="1" spans="1:20">
       <c r="A39" s="1" t="s">
         <v>87</v>
       </c>
@@ -4738,7 +5593,7 @@
         <v>110</v>
       </c>
       <c r="E39" s="1">
-        <v>202839.0</v>
+        <v>202839</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>29</v>
@@ -4783,7 +5638,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" customHeight="1" spans="1:20">
       <c r="A40" s="1" t="s">
         <v>87</v>
       </c>
@@ -4797,7 +5652,7 @@
         <v>110</v>
       </c>
       <c r="E40" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>36</v>
@@ -4842,7 +5697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" customHeight="1" spans="1:20">
       <c r="A41" s="1" t="s">
         <v>87</v>
       </c>
@@ -4856,7 +5711,7 @@
         <v>110</v>
       </c>
       <c r="E41" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>37</v>
@@ -4901,7 +5756,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" customHeight="1" spans="1:20">
       <c r="A42" s="1" t="s">
         <v>87</v>
       </c>
@@ -4915,7 +5770,7 @@
         <v>110</v>
       </c>
       <c r="E42" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>38</v>
@@ -4960,7 +5815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" customHeight="1" spans="1:20">
       <c r="A43" s="1" t="s">
         <v>87</v>
       </c>
@@ -4974,7 +5829,7 @@
         <v>120</v>
       </c>
       <c r="E43" s="1">
-        <v>4050.0</v>
+        <v>4050</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>29</v>
@@ -4992,25 +5847,25 @@
         <v>124</v>
       </c>
       <c r="L43" s="1">
-        <v>687.0</v>
+        <v>687</v>
       </c>
       <c r="M43" s="1">
-        <v>736.0</v>
+        <v>736</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O43" s="1">
-        <v>687.0</v>
+        <v>687</v>
       </c>
       <c r="P43" s="1">
-        <v>223.0</v>
+        <v>223</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R43" s="1">
-        <v>405.0</v>
+        <v>405</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>124</v>
@@ -5019,7 +5874,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" customHeight="1" spans="1:20">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -5033,52 +5888,52 @@
         <v>120</v>
       </c>
       <c r="E44" s="1">
-        <v>810.0</v>
+        <v>810</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="1">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="K44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="L44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="M44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O44" s="1">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="P44" s="1">
-        <v>648.0</v>
+        <v>648</v>
       </c>
       <c r="Q44" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="S44" s="1">
-        <v>689.0</v>
+        <v>689</v>
       </c>
       <c r="T44" s="1">
-        <v>689.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:20">
       <c r="A45" s="1" t="s">
         <v>87</v>
       </c>
@@ -5092,7 +5947,7 @@
         <v>120</v>
       </c>
       <c r="E45" s="1">
-        <v>199.0</v>
+        <v>199</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>37</v>
@@ -5107,37 +5962,37 @@
         <v>32</v>
       </c>
       <c r="K45" s="1">
-        <v>169.0</v>
+        <v>169</v>
       </c>
       <c r="L45" s="1">
-        <v>159.0</v>
+        <v>159</v>
       </c>
       <c r="M45" s="1">
-        <v>169.0</v>
+        <v>169</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O45" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P45" s="1">
-        <v>159.0</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R45" s="1">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="S45" s="1">
-        <v>169.0</v>
+        <v>169</v>
       </c>
       <c r="T45" s="1">
-        <v>169.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:20">
       <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
@@ -5151,7 +6006,7 @@
         <v>120</v>
       </c>
       <c r="E46" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>38</v>
@@ -5196,7 +6051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" customHeight="1" spans="1:20">
       <c r="A47" s="1" t="s">
         <v>87</v>
       </c>
@@ -5210,7 +6065,7 @@
         <v>126</v>
       </c>
       <c r="E47" s="1">
-        <v>469730.0</v>
+        <v>469730</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>29</v>
@@ -5255,7 +6110,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" customHeight="1" spans="1:20">
       <c r="A48" s="1" t="s">
         <v>87</v>
       </c>
@@ -5269,7 +6124,7 @@
         <v>126</v>
       </c>
       <c r="E48" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>36</v>
@@ -5314,7 +6169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" customHeight="1" spans="1:20">
       <c r="A49" s="1" t="s">
         <v>87</v>
       </c>
@@ -5328,7 +6183,7 @@
         <v>126</v>
       </c>
       <c r="E49" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>37</v>
@@ -5373,7 +6228,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" customHeight="1" spans="1:20">
       <c r="A50" s="1" t="s">
         <v>87</v>
       </c>
@@ -5387,7 +6242,7 @@
         <v>126</v>
       </c>
       <c r="E50" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>38</v>
@@ -5432,7 +6287,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" customHeight="1" spans="1:20">
       <c r="A51" s="1" t="s">
         <v>87</v>
       </c>
@@ -5446,7 +6301,7 @@
         <v>133</v>
       </c>
       <c r="E51" s="1">
-        <v>425504.0</v>
+        <v>425504</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>29</v>
@@ -5491,7 +6346,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" customHeight="1" spans="1:20">
       <c r="A52" s="1" t="s">
         <v>87</v>
       </c>
@@ -5505,7 +6360,7 @@
         <v>133</v>
       </c>
       <c r="E52" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>36</v>
@@ -5550,7 +6405,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" customHeight="1" spans="1:20">
       <c r="A53" s="1" t="s">
         <v>87</v>
       </c>
@@ -5564,7 +6419,7 @@
         <v>133</v>
       </c>
       <c r="E53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>37</v>
@@ -5579,13 +6434,13 @@
         <v>32</v>
       </c>
       <c r="K53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>32</v>
@@ -5594,7 +6449,7 @@
         <v>32</v>
       </c>
       <c r="P53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="1" t="s">
         <v>32</v>
@@ -5603,13 +6458,13 @@
         <v>32</v>
       </c>
       <c r="S53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="T53" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:20">
       <c r="A54" s="1" t="s">
         <v>87</v>
       </c>
@@ -5623,7 +6478,7 @@
         <v>133</v>
       </c>
       <c r="E54" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>38</v>
@@ -5668,7 +6523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" customHeight="1" spans="1:20">
       <c r="A55" s="1" t="s">
         <v>87</v>
       </c>
@@ -5682,7 +6537,7 @@
         <v>141</v>
       </c>
       <c r="E55" s="1">
-        <v>487531.0</v>
+        <v>487531</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>29</v>
@@ -5727,7 +6582,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" customHeight="1" spans="1:20">
       <c r="A56" s="1" t="s">
         <v>87</v>
       </c>
@@ -5741,7 +6596,7 @@
         <v>141</v>
       </c>
       <c r="E56" s="1">
-        <v>1199.0</v>
+        <v>1199</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>36</v>
@@ -5759,7 +6614,7 @@
         <v>149</v>
       </c>
       <c r="L56" s="1">
-        <v>959.0</v>
+        <v>959</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>149</v>
@@ -5768,10 +6623,10 @@
         <v>32</v>
       </c>
       <c r="O56" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="P56" s="1">
-        <v>959.0</v>
+        <v>959</v>
       </c>
       <c r="Q56" s="1" t="s">
         <v>32</v>
@@ -5786,7 +6641,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" customHeight="1" spans="1:20">
       <c r="A57" s="1" t="s">
         <v>87</v>
       </c>
@@ -5800,7 +6655,7 @@
         <v>141</v>
       </c>
       <c r="E57" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>37</v>
@@ -5845,7 +6700,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" customHeight="1" spans="1:20">
       <c r="A58" s="1" t="s">
         <v>87</v>
       </c>
@@ -5859,7 +6714,7 @@
         <v>141</v>
       </c>
       <c r="E58" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>38</v>
@@ -5904,7 +6759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" customHeight="1" spans="1:20">
       <c r="A59" s="1" t="s">
         <v>150</v>
       </c>
@@ -5918,7 +6773,7 @@
         <v>153</v>
       </c>
       <c r="E59" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>29</v>
@@ -5963,7 +6818,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" customHeight="1" spans="1:20">
       <c r="A60" s="1" t="s">
         <v>150</v>
       </c>
@@ -5977,7 +6832,7 @@
         <v>153</v>
       </c>
       <c r="E60" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>36</v>
@@ -6022,7 +6877,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" customHeight="1" spans="1:20">
       <c r="A61" s="1" t="s">
         <v>150</v>
       </c>
@@ -6036,7 +6891,7 @@
         <v>153</v>
       </c>
       <c r="E61" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>37</v>
@@ -6081,7 +6936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" customHeight="1" spans="1:20">
       <c r="A62" s="1" t="s">
         <v>150</v>
       </c>
@@ -6095,7 +6950,7 @@
         <v>153</v>
       </c>
       <c r="E62" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>38</v>
@@ -6140,7 +6995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" customHeight="1" spans="1:20">
       <c r="A63" s="1" t="s">
         <v>150</v>
       </c>
@@ -6154,7 +7009,7 @@
         <v>155</v>
       </c>
       <c r="E63" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>29</v>
@@ -6199,7 +7054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" customHeight="1" spans="1:20">
       <c r="A64" s="1" t="s">
         <v>150</v>
       </c>
@@ -6213,7 +7068,7 @@
         <v>155</v>
       </c>
       <c r="E64" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>36</v>
@@ -6258,7 +7113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" customHeight="1" spans="1:20">
       <c r="A65" s="1" t="s">
         <v>150</v>
       </c>
@@ -6272,7 +7127,7 @@
         <v>155</v>
       </c>
       <c r="E65" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>37</v>
@@ -6317,7 +7172,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" customHeight="1" spans="1:20">
       <c r="A66" s="1" t="s">
         <v>150</v>
       </c>
@@ -6331,7 +7186,7 @@
         <v>155</v>
       </c>
       <c r="E66" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>38</v>
@@ -6376,7 +7231,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" customHeight="1" spans="1:20">
       <c r="A67" s="1" t="s">
         <v>150</v>
       </c>
@@ -6390,7 +7245,7 @@
         <v>157</v>
       </c>
       <c r="E67" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>29</v>
@@ -6435,7 +7290,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" customHeight="1" spans="1:20">
       <c r="A68" s="1" t="s">
         <v>150</v>
       </c>
@@ -6449,7 +7304,7 @@
         <v>157</v>
       </c>
       <c r="E68" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>36</v>
@@ -6494,7 +7349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" customHeight="1" spans="1:20">
       <c r="A69" s="1" t="s">
         <v>150</v>
       </c>
@@ -6508,7 +7363,7 @@
         <v>157</v>
       </c>
       <c r="E69" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>37</v>
@@ -6553,7 +7408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" customHeight="1" spans="1:20">
       <c r="A70" s="1" t="s">
         <v>150</v>
       </c>
@@ -6567,7 +7422,7 @@
         <v>157</v>
       </c>
       <c r="E70" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>38</v>
@@ -6612,7 +7467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" customHeight="1" spans="1:20">
       <c r="A71" s="1" t="s">
         <v>150</v>
       </c>
@@ -6626,7 +7481,7 @@
         <v>159</v>
       </c>
       <c r="E71" s="1">
-        <v>3975.0</v>
+        <v>3975</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>29</v>
@@ -6656,7 +7511,7 @@
         <v>163</v>
       </c>
       <c r="P71" s="1">
-        <v>299.0</v>
+        <v>299</v>
       </c>
       <c r="Q71" s="1" t="s">
         <v>32</v>
@@ -6671,7 +7526,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" customHeight="1" spans="1:20">
       <c r="A72" s="1" t="s">
         <v>150</v>
       </c>
@@ -6685,37 +7540,37 @@
         <v>159</v>
       </c>
       <c r="E72" s="1">
-        <v>795.0</v>
+        <v>795</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H72" s="1">
-        <v>266.0</v>
+        <v>266</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J72" s="1">
-        <v>676.0</v>
+        <v>676</v>
       </c>
       <c r="K72" s="1">
-        <v>676.0</v>
+        <v>676</v>
       </c>
       <c r="L72" s="1">
-        <v>636.0</v>
+        <v>636</v>
       </c>
       <c r="M72" s="1">
-        <v>676.0</v>
+        <v>676</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O72" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="P72" s="1">
-        <v>636.0</v>
+        <v>636</v>
       </c>
       <c r="Q72" s="1" t="s">
         <v>32</v>
@@ -6724,13 +7579,13 @@
         <v>32</v>
       </c>
       <c r="S72" s="1">
-        <v>676.0</v>
+        <v>676</v>
       </c>
       <c r="T72" s="1">
-        <v>676.0</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:20">
       <c r="A73" s="1" t="s">
         <v>150</v>
       </c>
@@ -6744,7 +7599,7 @@
         <v>159</v>
       </c>
       <c r="E73" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>37</v>
@@ -6789,7 +7644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" customHeight="1" spans="1:20">
       <c r="A74" s="1" t="s">
         <v>150</v>
       </c>
@@ -6803,7 +7658,7 @@
         <v>159</v>
       </c>
       <c r="E74" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>38</v>
@@ -6848,7 +7703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" customHeight="1" spans="1:20">
       <c r="A75" s="1" t="s">
         <v>150</v>
       </c>
@@ -6862,7 +7717,7 @@
         <v>165</v>
       </c>
       <c r="E75" s="1">
-        <v>31332.0</v>
+        <v>31332</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>29</v>
@@ -6880,7 +7735,7 @@
         <v>168</v>
       </c>
       <c r="L75" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>169</v>
@@ -6889,16 +7744,16 @@
         <v>170</v>
       </c>
       <c r="O75" s="1">
-        <v>584.0</v>
+        <v>584</v>
       </c>
       <c r="P75" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="Q75" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R75" s="1">
-        <v>544.0</v>
+        <v>544</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>170</v>
@@ -6907,7 +7762,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" customHeight="1" spans="1:20">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -6921,7 +7776,7 @@
         <v>165</v>
       </c>
       <c r="E76" s="1">
-        <v>2176.0</v>
+        <v>2176</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>36</v>
@@ -6948,7 +7803,7 @@
         <v>32</v>
       </c>
       <c r="O76" s="1">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>172</v>
@@ -6966,7 +7821,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" customHeight="1" spans="1:20">
       <c r="A77" s="1" t="s">
         <v>150</v>
       </c>
@@ -6980,7 +7835,7 @@
         <v>165</v>
       </c>
       <c r="E77" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>37</v>
@@ -7025,7 +7880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" customHeight="1" spans="1:20">
       <c r="A78" s="1" t="s">
         <v>150</v>
       </c>
@@ -7039,7 +7894,7 @@
         <v>165</v>
       </c>
       <c r="E78" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>38</v>
@@ -7084,7 +7939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" customHeight="1" spans="1:20">
       <c r="A79" s="1" t="s">
         <v>150</v>
       </c>
@@ -7098,7 +7953,7 @@
         <v>175</v>
       </c>
       <c r="E79" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>29</v>
@@ -7143,7 +7998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" customHeight="1" spans="1:20">
       <c r="A80" s="1" t="s">
         <v>150</v>
       </c>
@@ -7157,7 +8012,7 @@
         <v>175</v>
       </c>
       <c r="E80" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>36</v>
@@ -7202,7 +8057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" customHeight="1" spans="1:20">
       <c r="A81" s="1" t="s">
         <v>150</v>
       </c>
@@ -7216,7 +8071,7 @@
         <v>175</v>
       </c>
       <c r="E81" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>37</v>
@@ -7261,7 +8116,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" customHeight="1" spans="1:20">
       <c r="A82" s="1" t="s">
         <v>150</v>
       </c>
@@ -7275,7 +8130,7 @@
         <v>175</v>
       </c>
       <c r="E82" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>38</v>
@@ -7320,7 +8175,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" customHeight="1" spans="1:20">
       <c r="A83" s="1" t="s">
         <v>150</v>
       </c>
@@ -7334,7 +8189,7 @@
         <v>177</v>
       </c>
       <c r="E83" s="1">
-        <v>337296.0</v>
+        <v>337296</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>29</v>
@@ -7379,7 +8234,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" customHeight="1" spans="1:20">
       <c r="A84" s="1" t="s">
         <v>150</v>
       </c>
@@ -7393,7 +8248,7 @@
         <v>177</v>
       </c>
       <c r="E84" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>36</v>
@@ -7438,7 +8293,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" customHeight="1" spans="1:20">
       <c r="A85" s="1" t="s">
         <v>150</v>
       </c>
@@ -7452,7 +8307,7 @@
         <v>177</v>
       </c>
       <c r="E85" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>37</v>
@@ -7497,7 +8352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" customHeight="1" spans="1:20">
       <c r="A86" s="1" t="s">
         <v>150</v>
       </c>
@@ -7511,7 +8366,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>38</v>
@@ -7556,7 +8411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" customHeight="1" spans="1:20">
       <c r="A87" s="1" t="s">
         <v>187</v>
       </c>
@@ -7570,7 +8425,7 @@
         <v>190</v>
       </c>
       <c r="E87" s="1">
-        <v>291832.0</v>
+        <v>291832</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>29</v>
@@ -7615,7 +8470,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" customHeight="1" spans="1:20">
       <c r="A88" s="1" t="s">
         <v>187</v>
       </c>
@@ -7629,37 +8484,37 @@
         <v>190</v>
       </c>
       <c r="E88" s="1">
-        <v>441.0</v>
+        <v>441</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H88" s="1">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J88" s="1">
-        <v>375.0</v>
+        <v>375</v>
       </c>
       <c r="K88" s="1">
-        <v>375.0</v>
+        <v>375</v>
       </c>
       <c r="L88" s="1">
-        <v>353.0</v>
+        <v>353</v>
       </c>
       <c r="M88" s="1">
-        <v>375.0</v>
+        <v>375</v>
       </c>
       <c r="N88" s="1">
-        <v>190.0</v>
+        <v>190</v>
       </c>
       <c r="O88" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="P88" s="1">
-        <v>353.0</v>
+        <v>353</v>
       </c>
       <c r="Q88" s="1" t="s">
         <v>32</v>
@@ -7668,13 +8523,13 @@
         <v>32</v>
       </c>
       <c r="S88" s="1">
-        <v>375.0</v>
+        <v>375</v>
       </c>
       <c r="T88" s="1">
-        <v>375.0</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:20">
       <c r="A89" s="1" t="s">
         <v>187</v>
       </c>
@@ -7688,7 +8543,7 @@
         <v>190</v>
       </c>
       <c r="E89" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -7703,22 +8558,22 @@
         <v>32</v>
       </c>
       <c r="K89" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="L89" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="M89" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="N89" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O89" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>32</v>
@@ -7727,13 +8582,13 @@
         <v>32</v>
       </c>
       <c r="S89" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="T89" s="1">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:20">
       <c r="A90" s="1" t="s">
         <v>187</v>
       </c>
@@ -7747,7 +8602,7 @@
         <v>190</v>
       </c>
       <c r="E90" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>38</v>
@@ -7792,7 +8647,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" customHeight="1" spans="1:20">
       <c r="A91" s="1" t="s">
         <v>187</v>
       </c>
@@ -7806,7 +8661,7 @@
         <v>200</v>
       </c>
       <c r="E91" s="1">
-        <v>400624.0</v>
+        <v>400624</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>29</v>
@@ -7851,7 +8706,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" customHeight="1" spans="1:20">
       <c r="A92" s="1" t="s">
         <v>187</v>
       </c>
@@ -7865,7 +8720,7 @@
         <v>200</v>
       </c>
       <c r="E92" s="1">
-        <v>7464.0</v>
+        <v>7464</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>36</v>
@@ -7910,7 +8765,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" customHeight="1" spans="1:20">
       <c r="A93" s="1" t="s">
         <v>187</v>
       </c>
@@ -7924,7 +8779,7 @@
         <v>200</v>
       </c>
       <c r="E93" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>37</v>
@@ -7939,37 +8794,37 @@
         <v>32</v>
       </c>
       <c r="K93" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="L93" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="M93" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="N93" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O93" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P93" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="Q93" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R93" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="S93" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="T93" s="1">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:20">
       <c r="A94" s="1" t="s">
         <v>187</v>
       </c>
@@ -7983,7 +8838,7 @@
         <v>200</v>
       </c>
       <c r="E94" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>38</v>
@@ -8028,7 +8883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" customHeight="1" spans="1:20">
       <c r="A95" s="1" t="s">
         <v>187</v>
       </c>
@@ -8042,7 +8897,7 @@
         <v>216</v>
       </c>
       <c r="E95" s="1">
-        <v>326511.0</v>
+        <v>326511</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>29</v>
@@ -8087,7 +8942,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" customHeight="1" spans="1:20">
       <c r="A96" s="1" t="s">
         <v>187</v>
       </c>
@@ -8101,7 +8956,7 @@
         <v>216</v>
       </c>
       <c r="E96" s="1">
-        <v>13101.0</v>
+        <v>13101</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>36</v>
@@ -8146,7 +9001,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" customHeight="1" spans="1:20">
       <c r="A97" s="1" t="s">
         <v>187</v>
       </c>
@@ -8160,7 +9015,7 @@
         <v>216</v>
       </c>
       <c r="E97" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>37</v>
@@ -8205,7 +9060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" customHeight="1" spans="1:20">
       <c r="A98" s="1" t="s">
         <v>187</v>
       </c>
@@ -8219,7 +9074,7 @@
         <v>216</v>
       </c>
       <c r="E98" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>38</v>
@@ -8234,37 +9089,37 @@
         <v>32</v>
       </c>
       <c r="K98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N98" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O98" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="Q98" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R98" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="S98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="T98" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:20">
       <c r="A99" s="1" t="s">
         <v>187</v>
       </c>
@@ -8278,7 +9133,7 @@
         <v>233</v>
       </c>
       <c r="E99" s="1">
-        <v>467873.0</v>
+        <v>467873</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>29</v>
@@ -8323,7 +9178,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" customHeight="1" spans="1:20">
       <c r="A100" s="1" t="s">
         <v>187</v>
       </c>
@@ -8337,7 +9192,7 @@
         <v>233</v>
       </c>
       <c r="E100" s="1">
-        <v>19334.0</v>
+        <v>19334</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>36</v>
@@ -8382,7 +9237,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" customHeight="1" spans="1:20">
       <c r="A101" s="1" t="s">
         <v>187</v>
       </c>
@@ -8396,7 +9251,7 @@
         <v>233</v>
       </c>
       <c r="E101" s="1">
-        <v>1048.0</v>
+        <v>1048</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>37</v>
@@ -8411,37 +9266,37 @@
         <v>32</v>
       </c>
       <c r="K101" s="1">
-        <v>891.0</v>
+        <v>891</v>
       </c>
       <c r="L101" s="1">
-        <v>838.0</v>
+        <v>838</v>
       </c>
       <c r="M101" s="1">
-        <v>891.0</v>
+        <v>891</v>
       </c>
       <c r="N101" s="1">
-        <v>355.0</v>
+        <v>355</v>
       </c>
       <c r="O101" s="1">
-        <v>227.0</v>
+        <v>227</v>
       </c>
       <c r="P101" s="1">
-        <v>838.0</v>
+        <v>838</v>
       </c>
       <c r="Q101" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R101" s="1">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="S101" s="1">
-        <v>891.0</v>
+        <v>891</v>
       </c>
       <c r="T101" s="1">
-        <v>891.0</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:20">
       <c r="A102" s="1" t="s">
         <v>187</v>
       </c>
@@ -8455,7 +9310,7 @@
         <v>233</v>
       </c>
       <c r="E102" s="1">
-        <v>36643.0</v>
+        <v>36643</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>38</v>
@@ -8500,7 +9355,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" customHeight="1" spans="1:20">
       <c r="A103" s="1" t="s">
         <v>187</v>
       </c>
@@ -8514,7 +9369,7 @@
         <v>256</v>
       </c>
       <c r="E103" s="1">
-        <v>466254.0</v>
+        <v>466254</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>29</v>
@@ -8559,7 +9414,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" customHeight="1" spans="1:20">
       <c r="A104" s="1" t="s">
         <v>187</v>
       </c>
@@ -8573,7 +9428,7 @@
         <v>256</v>
       </c>
       <c r="E104" s="1">
-        <v>12876.0</v>
+        <v>12876</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>36</v>
@@ -8600,7 +9455,7 @@
         <v>269</v>
       </c>
       <c r="O104" s="1">
-        <v>781.0</v>
+        <v>781</v>
       </c>
       <c r="P104" s="1" t="s">
         <v>268</v>
@@ -8618,7 +9473,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" customHeight="1" spans="1:20">
       <c r="A105" s="1" t="s">
         <v>187</v>
       </c>
@@ -8632,7 +9487,7 @@
         <v>256</v>
       </c>
       <c r="E105" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>37</v>
@@ -8647,37 +9502,37 @@
         <v>32</v>
       </c>
       <c r="K105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N105" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O105" s="1" t="s">
         <v>32</v>
       </c>
       <c r="P105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="Q105" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R105" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="S105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="T105" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:20">
       <c r="A106" s="1" t="s">
         <v>187</v>
       </c>
@@ -8691,7 +9546,7 @@
         <v>256</v>
       </c>
       <c r="E106" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>38</v>
@@ -8736,7 +9591,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" customHeight="1" spans="1:20">
       <c r="A107" s="1" t="s">
         <v>187</v>
       </c>
@@ -8750,7 +9605,7 @@
         <v>270</v>
       </c>
       <c r="E107" s="1">
-        <v>98903.0</v>
+        <v>98903</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>29</v>
@@ -8795,7 +9650,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" customHeight="1" spans="1:20">
       <c r="A108" s="1" t="s">
         <v>187</v>
       </c>
@@ -8809,7 +9664,7 @@
         <v>270</v>
       </c>
       <c r="E108" s="1">
-        <v>11121.0</v>
+        <v>11121</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>36</v>
@@ -8854,7 +9709,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" customHeight="1" spans="1:20">
       <c r="A109" s="1" t="s">
         <v>187</v>
       </c>
@@ -8868,7 +9723,7 @@
         <v>270</v>
       </c>
       <c r="E109" s="1">
-        <v>195.0</v>
+        <v>195</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>37</v>
@@ -8883,37 +9738,37 @@
         <v>32</v>
       </c>
       <c r="K109" s="1">
-        <v>166.0</v>
+        <v>166</v>
       </c>
       <c r="L109" s="1">
-        <v>156.0</v>
+        <v>156</v>
       </c>
       <c r="M109" s="1">
-        <v>166.0</v>
+        <v>166</v>
       </c>
       <c r="N109" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="O109" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="P109" s="1">
-        <v>156.0</v>
+        <v>156</v>
       </c>
       <c r="Q109" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R109" s="1">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="S109" s="1">
-        <v>166.0</v>
+        <v>166</v>
       </c>
       <c r="T109" s="1">
-        <v>166.0</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:20">
       <c r="A110" s="1" t="s">
         <v>187</v>
       </c>
@@ -8927,7 +9782,7 @@
         <v>270</v>
       </c>
       <c r="E110" s="1">
-        <v>690.0</v>
+        <v>690</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>38</v>
@@ -8942,37 +9797,37 @@
         <v>32</v>
       </c>
       <c r="K110" s="1">
-        <v>587.0</v>
+        <v>587</v>
       </c>
       <c r="L110" s="1">
-        <v>552.0</v>
+        <v>552</v>
       </c>
       <c r="M110" s="1">
-        <v>587.0</v>
+        <v>587</v>
       </c>
       <c r="N110" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="O110" s="1">
-        <v>261.0</v>
+        <v>261</v>
       </c>
       <c r="P110" s="1">
-        <v>552.0</v>
+        <v>552</v>
       </c>
       <c r="Q110" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R110" s="1">
-        <v>240.0</v>
+        <v>240</v>
       </c>
       <c r="S110" s="1">
-        <v>587.0</v>
+        <v>587</v>
       </c>
       <c r="T110" s="1">
-        <v>587.0</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:20">
       <c r="A111" s="1" t="s">
         <v>187</v>
       </c>
@@ -8986,7 +9841,7 @@
         <v>287</v>
       </c>
       <c r="E111" s="1">
-        <v>310842.0</v>
+        <v>310842</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>29</v>
@@ -9031,7 +9886,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" customHeight="1" spans="1:20">
       <c r="A112" s="1" t="s">
         <v>187</v>
       </c>
@@ -9045,7 +9900,7 @@
         <v>287</v>
       </c>
       <c r="E112" s="1">
-        <v>7271.0</v>
+        <v>7271</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>36</v>
@@ -9072,7 +9927,7 @@
         <v>301</v>
       </c>
       <c r="O112" s="1">
-        <v>397.0</v>
+        <v>397</v>
       </c>
       <c r="P112" s="1" t="s">
         <v>300</v>
@@ -9090,7 +9945,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" customHeight="1" spans="1:20">
       <c r="A113" s="1" t="s">
         <v>187</v>
       </c>
@@ -9104,7 +9959,7 @@
         <v>287</v>
       </c>
       <c r="E113" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>37</v>
@@ -9146,7 +10001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" customHeight="1" spans="1:20">
       <c r="A114" s="1" t="s">
         <v>187</v>
       </c>
@@ -9160,7 +10015,7 @@
         <v>287</v>
       </c>
       <c r="E114" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>38</v>
@@ -9202,7 +10057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" customHeight="1" spans="1:20">
       <c r="A115" s="1" t="s">
         <v>303</v>
       </c>
@@ -9216,7 +10071,7 @@
         <v>306</v>
       </c>
       <c r="E115" s="1">
-        <v>273468.0</v>
+        <v>273468</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>29</v>
@@ -9261,7 +10116,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" customHeight="1" spans="1:20">
       <c r="A116" s="1" t="s">
         <v>303</v>
       </c>
@@ -9275,7 +10130,7 @@
         <v>306</v>
       </c>
       <c r="E116" s="1">
-        <v>23445.0</v>
+        <v>23445</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>36</v>
@@ -9320,7 +10175,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" customHeight="1" spans="1:20">
       <c r="A117" s="1" t="s">
         <v>303</v>
       </c>
@@ -9334,7 +10189,7 @@
         <v>306</v>
       </c>
       <c r="E117" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>37</v>
@@ -9346,37 +10201,37 @@
         <v>32</v>
       </c>
       <c r="K117" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="L117" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="M117" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="N117" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="O117" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P117" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="Q117" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R117" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="S117" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="T117" s="1">
-        <v>43.0</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:20">
       <c r="A118" s="1" t="s">
         <v>303</v>
       </c>
@@ -9390,7 +10245,7 @@
         <v>306</v>
       </c>
       <c r="E118" s="1">
-        <v>21248.0</v>
+        <v>21248</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>38</v>
@@ -9432,7 +10287,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" customHeight="1" spans="1:20">
       <c r="A119" s="1" t="s">
         <v>303</v>
       </c>
@@ -9446,7 +10301,7 @@
         <v>327</v>
       </c>
       <c r="E119" s="1">
-        <v>242847.0</v>
+        <v>242847</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>29</v>
@@ -9491,7 +10346,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" customHeight="1" spans="1:20">
       <c r="A120" s="1" t="s">
         <v>303</v>
       </c>
@@ -9505,7 +10360,7 @@
         <v>327</v>
       </c>
       <c r="E120" s="1">
-        <v>18505.0</v>
+        <v>18505</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>36</v>
@@ -9550,7 +10405,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" customHeight="1" spans="1:20">
       <c r="A121" s="1" t="s">
         <v>303</v>
       </c>
@@ -9564,7 +10419,7 @@
         <v>327</v>
       </c>
       <c r="E121" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>37</v>
@@ -9606,7 +10461,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" customHeight="1" spans="1:20">
       <c r="A122" s="1" t="s">
         <v>303</v>
       </c>
@@ -9620,7 +10475,7 @@
         <v>327</v>
       </c>
       <c r="E122" s="1">
-        <v>9898.0</v>
+        <v>9898</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>38</v>
@@ -9644,7 +10499,7 @@
         <v>345</v>
       </c>
       <c r="O122" s="1">
-        <v>624.0</v>
+        <v>624</v>
       </c>
       <c r="P122" s="1" t="s">
         <v>344</v>
@@ -9662,7 +10517,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" customHeight="1" spans="1:20">
       <c r="A123" s="1" t="s">
         <v>303</v>
       </c>
@@ -9676,7 +10531,7 @@
         <v>348</v>
       </c>
       <c r="E123" s="1">
-        <v>209416.0</v>
+        <v>209416</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>29</v>
@@ -9721,7 +10576,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" customHeight="1" spans="1:20">
       <c r="A124" s="1" t="s">
         <v>303</v>
       </c>
@@ -9735,13 +10590,13 @@
         <v>348</v>
       </c>
       <c r="E124" s="1">
-        <v>2999.0</v>
+        <v>2999</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H124" s="1">
-        <v>627.0</v>
+        <v>627</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>32</v>
@@ -9762,7 +10617,7 @@
         <v>359</v>
       </c>
       <c r="O124" s="1">
-        <v>694.0</v>
+        <v>694</v>
       </c>
       <c r="P124" s="1" t="s">
         <v>360</v>
@@ -9780,7 +10635,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" customHeight="1" spans="1:20">
       <c r="A125" s="1" t="s">
         <v>303</v>
       </c>
@@ -9794,7 +10649,7 @@
         <v>348</v>
       </c>
       <c r="E125" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>37</v>
@@ -9836,7 +10691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" customHeight="1" spans="1:20">
       <c r="A126" s="1" t="s">
         <v>303</v>
       </c>
@@ -9850,7 +10705,7 @@
         <v>348</v>
       </c>
       <c r="E126" s="1">
-        <v>484.0</v>
+        <v>484</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>38</v>
@@ -9862,37 +10717,37 @@
         <v>32</v>
       </c>
       <c r="K126" s="1">
-        <v>411.0</v>
+        <v>411</v>
       </c>
       <c r="L126" s="1">
-        <v>387.0</v>
+        <v>387</v>
       </c>
       <c r="M126" s="1">
-        <v>411.0</v>
+        <v>411</v>
       </c>
       <c r="N126" s="1">
-        <v>244.0</v>
+        <v>244</v>
       </c>
       <c r="O126" s="1">
-        <v>122.0</v>
+        <v>122</v>
       </c>
       <c r="P126" s="1">
-        <v>387.0</v>
+        <v>387</v>
       </c>
       <c r="Q126" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R126" s="1">
-        <v>344.0</v>
+        <v>344</v>
       </c>
       <c r="S126" s="1">
-        <v>411.0</v>
+        <v>411</v>
       </c>
       <c r="T126" s="1">
-        <v>411.0</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:20">
       <c r="A127" s="1" t="s">
         <v>303</v>
       </c>
@@ -9906,7 +10761,7 @@
         <v>362</v>
       </c>
       <c r="E127" s="1">
-        <v>239904.0</v>
+        <v>239904</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>29</v>
@@ -9951,7 +10806,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" customHeight="1" spans="1:20">
       <c r="A128" s="1" t="s">
         <v>303</v>
       </c>
@@ -9965,52 +10820,52 @@
         <v>362</v>
       </c>
       <c r="E128" s="1">
-        <v>324.0</v>
+        <v>324</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H128" s="1">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="K128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="L128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="M128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="N128" s="1">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="O128" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="P128" s="1">
-        <v>259.0</v>
+        <v>259</v>
       </c>
       <c r="Q128" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="S128" s="1">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="T128" s="1">
-        <v>275.0</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:20">
       <c r="A129" s="1" t="s">
         <v>303</v>
       </c>
@@ -10024,7 +10879,7 @@
         <v>362</v>
       </c>
       <c r="E129" s="1">
-        <v>3498.0</v>
+        <v>3498</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>37</v>
@@ -10045,10 +10900,10 @@
         <v>373</v>
       </c>
       <c r="N129" s="1">
-        <v>813.0</v>
+        <v>813</v>
       </c>
       <c r="O129" s="1">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="P129" s="1" t="s">
         <v>374</v>
@@ -10066,7 +10921,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" customHeight="1" spans="1:20">
       <c r="A130" s="1" t="s">
         <v>303</v>
       </c>
@@ -10080,7 +10935,7 @@
         <v>362</v>
       </c>
       <c r="E130" s="1">
-        <v>8314.0</v>
+        <v>8314</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>38</v>
@@ -10104,7 +10959,7 @@
         <v>378</v>
       </c>
       <c r="O130" s="1">
-        <v>524.0</v>
+        <v>524</v>
       </c>
       <c r="P130" s="1" t="s">
         <v>377</v>
@@ -10122,7 +10977,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" customHeight="1" spans="1:20">
       <c r="A131" s="1" t="s">
         <v>303</v>
       </c>
@@ -10136,7 +10991,7 @@
         <v>381</v>
       </c>
       <c r="E131" s="1">
-        <v>352678.0</v>
+        <v>352678</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>29</v>
@@ -10181,7 +11036,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" customHeight="1" spans="1:20">
       <c r="A132" s="1" t="s">
         <v>303</v>
       </c>
@@ -10195,13 +11050,13 @@
         <v>381</v>
       </c>
       <c r="E132" s="1">
-        <v>9233.0</v>
+        <v>9233</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H132" s="1">
-        <v>770.0</v>
+        <v>770</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>32</v>
@@ -10222,7 +11077,7 @@
         <v>393</v>
       </c>
       <c r="O132" s="1">
-        <v>545.0</v>
+        <v>545</v>
       </c>
       <c r="P132" s="1" t="s">
         <v>394</v>
@@ -10240,7 +11095,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" customHeight="1" spans="1:20">
       <c r="A133" s="1" t="s">
         <v>303</v>
       </c>
@@ -10254,7 +11109,7 @@
         <v>381</v>
       </c>
       <c r="E133" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>37</v>
@@ -10266,37 +11121,37 @@
         <v>32</v>
       </c>
       <c r="K133" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="L133" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="M133" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="N133" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="O133" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P133" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="Q133" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R133" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="S133" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="T133" s="1">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:20">
       <c r="A134" s="1" t="s">
         <v>303</v>
       </c>
@@ -10310,7 +11165,7 @@
         <v>381</v>
       </c>
       <c r="E134" s="1">
-        <v>9494.0</v>
+        <v>9494</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>38</v>
@@ -10334,7 +11189,7 @@
         <v>397</v>
       </c>
       <c r="O134" s="1">
-        <v>598.0</v>
+        <v>598</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>396</v>
@@ -10352,7 +11207,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" customHeight="1" spans="1:20">
       <c r="A135" s="1" t="s">
         <v>303</v>
       </c>
@@ -10366,7 +11221,7 @@
         <v>399</v>
       </c>
       <c r="E135" s="1">
-        <v>320572.0</v>
+        <v>320572</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>29</v>
@@ -10411,7 +11266,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" customHeight="1" spans="1:20">
       <c r="A136" s="1" t="s">
         <v>303</v>
       </c>
@@ -10425,7 +11280,7 @@
         <v>399</v>
       </c>
       <c r="E136" s="1">
-        <v>52507.0</v>
+        <v>52507</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>36</v>
@@ -10470,7 +11325,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" customHeight="1" spans="1:20">
       <c r="A137" s="1" t="s">
         <v>303</v>
       </c>
@@ -10484,7 +11339,7 @@
         <v>399</v>
       </c>
       <c r="E137" s="1">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>37</v>
@@ -10496,37 +11351,37 @@
         <v>32</v>
       </c>
       <c r="K137" s="1">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="L137" s="1">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="M137" s="1">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="N137" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="O137" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="P137" s="1">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="Q137" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R137" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="S137" s="1">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="T137" s="1">
-        <v>125.0</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:20">
       <c r="A138" s="1" t="s">
         <v>303</v>
       </c>
@@ -10540,7 +11395,7 @@
         <v>399</v>
       </c>
       <c r="E138" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>38</v>
@@ -10582,7 +11437,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" customHeight="1" spans="1:20">
       <c r="A139" s="1" t="s">
         <v>303</v>
       </c>
@@ -10596,7 +11451,7 @@
         <v>415</v>
       </c>
       <c r="E139" s="1">
-        <v>160769.0</v>
+        <v>160769</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>29</v>
@@ -10641,7 +11496,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" customHeight="1" spans="1:20">
       <c r="A140" s="1" t="s">
         <v>303</v>
       </c>
@@ -10655,7 +11510,7 @@
         <v>415</v>
       </c>
       <c r="E140" s="1">
-        <v>5313.0</v>
+        <v>5313</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>36</v>
@@ -10682,7 +11537,7 @@
         <v>426</v>
       </c>
       <c r="O140" s="1">
-        <v>291.0</v>
+        <v>291</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>427</v>
@@ -10700,7 +11555,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" customHeight="1" spans="1:20">
       <c r="A141" s="1" t="s">
         <v>303</v>
       </c>
@@ -10714,7 +11569,7 @@
         <v>415</v>
       </c>
       <c r="E141" s="1">
-        <v>214.0</v>
+        <v>214</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>37</v>
@@ -10726,37 +11581,37 @@
         <v>32</v>
       </c>
       <c r="K141" s="1">
-        <v>182.0</v>
+        <v>182</v>
       </c>
       <c r="L141" s="1">
-        <v>171.0</v>
+        <v>171</v>
       </c>
       <c r="M141" s="1">
-        <v>182.0</v>
+        <v>182</v>
       </c>
       <c r="N141" s="1">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="O141" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P141" s="1">
-        <v>171.0</v>
+        <v>171</v>
       </c>
       <c r="Q141" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R141" s="1">
-        <v>171.0</v>
+        <v>171</v>
       </c>
       <c r="S141" s="1">
-        <v>182.0</v>
+        <v>182</v>
       </c>
       <c r="T141" s="1">
-        <v>182.0</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:20">
       <c r="A142" s="1" t="s">
         <v>303</v>
       </c>
@@ -10770,7 +11625,7 @@
         <v>415</v>
       </c>
       <c r="E142" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>38</v>
@@ -10812,7 +11667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" customHeight="1" spans="1:20">
       <c r="A143" s="1" t="s">
         <v>303</v>
       </c>
@@ -10826,7 +11681,7 @@
         <v>429</v>
       </c>
       <c r="E143" s="1">
-        <v>105798.0</v>
+        <v>105798</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>29</v>
@@ -10871,7 +11726,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" customHeight="1" spans="1:20">
       <c r="A144" s="1" t="s">
         <v>303</v>
       </c>
@@ -10885,7 +11740,7 @@
         <v>429</v>
       </c>
       <c r="E144" s="1">
-        <v>4421.0</v>
+        <v>4421</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>36</v>
@@ -10930,7 +11785,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" customHeight="1" spans="1:20">
       <c r="A145" s="1" t="s">
         <v>303</v>
       </c>
@@ -10944,7 +11799,7 @@
         <v>429</v>
       </c>
       <c r="E145" s="1">
-        <v>347.0</v>
+        <v>347</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>37</v>
@@ -10956,37 +11811,37 @@
         <v>32</v>
       </c>
       <c r="K145" s="1">
-        <v>295.0</v>
+        <v>295</v>
       </c>
       <c r="L145" s="1">
-        <v>278.0</v>
+        <v>278</v>
       </c>
       <c r="M145" s="1">
-        <v>295.0</v>
+        <v>295</v>
       </c>
       <c r="N145" s="1">
-        <v>175.0</v>
+        <v>175</v>
       </c>
       <c r="O145" s="1">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="P145" s="1">
-        <v>278.0</v>
+        <v>278</v>
       </c>
       <c r="Q145" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R145" s="1">
-        <v>209.0</v>
+        <v>209</v>
       </c>
       <c r="S145" s="1">
-        <v>295.0</v>
+        <v>295</v>
       </c>
       <c r="T145" s="1">
-        <v>295.0</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:20">
       <c r="A146" s="1" t="s">
         <v>303</v>
       </c>
@@ -11000,7 +11855,7 @@
         <v>429</v>
       </c>
       <c r="E146" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>38</v>
@@ -11042,7 +11897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" customHeight="1" spans="1:20">
       <c r="A147" s="1" t="s">
         <v>443</v>
       </c>
@@ -11056,7 +11911,7 @@
         <v>446</v>
       </c>
       <c r="E147" s="1">
-        <v>169084.0</v>
+        <v>169084</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>29</v>
@@ -11101,7 +11956,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" customHeight="1" spans="1:20">
       <c r="A148" s="1" t="s">
         <v>443</v>
       </c>
@@ -11115,7 +11970,7 @@
         <v>446</v>
       </c>
       <c r="E148" s="1">
-        <v>4934.0</v>
+        <v>4934</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>36</v>
@@ -11142,7 +11997,7 @@
         <v>32</v>
       </c>
       <c r="O148" s="1">
-        <v>848.0</v>
+        <v>848</v>
       </c>
       <c r="P148" s="1" t="s">
         <v>456</v>
@@ -11160,7 +12015,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" customHeight="1" spans="1:20">
       <c r="A149" s="1" t="s">
         <v>443</v>
       </c>
@@ -11174,7 +12029,7 @@
         <v>446</v>
       </c>
       <c r="E149" s="1">
-        <v>2409.0</v>
+        <v>2409</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>37</v>
@@ -11195,10 +12050,10 @@
         <v>457</v>
       </c>
       <c r="N149" s="1">
-        <v>646.0</v>
+        <v>646</v>
       </c>
       <c r="O149" s="1">
-        <v>193.0</v>
+        <v>193</v>
       </c>
       <c r="P149" s="1" t="s">
         <v>458</v>
@@ -11216,7 +12071,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" customHeight="1" spans="1:20">
       <c r="A150" s="1" t="s">
         <v>443</v>
       </c>
@@ -11230,7 +12085,7 @@
         <v>446</v>
       </c>
       <c r="E150" s="1">
-        <v>3977.0</v>
+        <v>3977</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>38</v>
@@ -11254,7 +12109,7 @@
         <v>462</v>
       </c>
       <c r="O150" s="1">
-        <v>752.0</v>
+        <v>752</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>461</v>
@@ -11272,7 +12127,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" customHeight="1" spans="1:20">
       <c r="A151" s="1" t="s">
         <v>443</v>
       </c>
@@ -11286,7 +12141,7 @@
         <v>465</v>
       </c>
       <c r="E151" s="1">
-        <v>231183.0</v>
+        <v>231183</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>29</v>
@@ -11331,7 +12186,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" customHeight="1" spans="1:20">
       <c r="A152" s="1" t="s">
         <v>443</v>
       </c>
@@ -11345,7 +12200,7 @@
         <v>465</v>
       </c>
       <c r="E152" s="1">
-        <v>5591.0</v>
+        <v>5591</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>36</v>
@@ -11372,7 +12227,7 @@
         <v>477</v>
       </c>
       <c r="O152" s="1">
-        <v>321.0</v>
+        <v>321</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>478</v>
@@ -11390,7 +12245,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" customHeight="1" spans="1:20">
       <c r="A153" s="1" t="s">
         <v>443</v>
       </c>
@@ -11404,7 +12259,7 @@
         <v>465</v>
       </c>
       <c r="E153" s="1">
-        <v>6778.0</v>
+        <v>6778</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>37</v>
@@ -11428,7 +12283,7 @@
         <v>481</v>
       </c>
       <c r="O153" s="1">
-        <v>273.0</v>
+        <v>273</v>
       </c>
       <c r="P153" s="1" t="s">
         <v>482</v>
@@ -11446,7 +12301,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" customHeight="1" spans="1:20">
       <c r="A154" s="1" t="s">
         <v>443</v>
       </c>
@@ -11460,7 +12315,7 @@
         <v>465</v>
       </c>
       <c r="E154" s="1">
-        <v>5400.0</v>
+        <v>5400</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>38</v>
@@ -11484,7 +12339,7 @@
         <v>485</v>
       </c>
       <c r="O154" s="1">
-        <v>340.0</v>
+        <v>340</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>484</v>
@@ -11502,7 +12357,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" customHeight="1" spans="1:20">
       <c r="A155" s="1" t="s">
         <v>443</v>
       </c>
@@ -11516,7 +12371,7 @@
         <v>488</v>
       </c>
       <c r="E155" s="1">
-        <v>159379.0</v>
+        <v>159379</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>29</v>
@@ -11561,7 +12416,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" customHeight="1" spans="1:20">
       <c r="A156" s="1" t="s">
         <v>443</v>
       </c>
@@ -11575,7 +12430,7 @@
         <v>488</v>
       </c>
       <c r="E156" s="1">
-        <v>8623.0</v>
+        <v>8623</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>36</v>
@@ -11620,7 +12475,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" customHeight="1" spans="1:20">
       <c r="A157" s="1" t="s">
         <v>443</v>
       </c>
@@ -11634,7 +12489,7 @@
         <v>488</v>
       </c>
       <c r="E157" s="1">
-        <v>12530.0</v>
+        <v>12530</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>37</v>
@@ -11676,7 +12531,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" customHeight="1" spans="1:20">
       <c r="A158" s="1" t="s">
         <v>443</v>
       </c>
@@ -11690,7 +12545,7 @@
         <v>488</v>
       </c>
       <c r="E158" s="1">
-        <v>2129.0</v>
+        <v>2129</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>38</v>
@@ -11714,7 +12569,7 @@
         <v>510</v>
       </c>
       <c r="O158" s="1">
-        <v>805.0</v>
+        <v>805</v>
       </c>
       <c r="P158" s="1" t="s">
         <v>509</v>
@@ -11732,7 +12587,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" customHeight="1" spans="1:20">
       <c r="A159" s="1" t="s">
         <v>443</v>
       </c>
@@ -11746,7 +12601,7 @@
         <v>513</v>
       </c>
       <c r="E159" s="1">
-        <v>262629.0</v>
+        <v>262629</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>29</v>
@@ -11791,7 +12646,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" customHeight="1" spans="1:20">
       <c r="A160" s="1" t="s">
         <v>443</v>
       </c>
@@ -11805,7 +12660,7 @@
         <v>513</v>
       </c>
       <c r="E160" s="1">
-        <v>6678.0</v>
+        <v>6678</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>36</v>
@@ -11832,7 +12687,7 @@
         <v>32</v>
       </c>
       <c r="O160" s="1">
-        <v>379.0</v>
+        <v>379</v>
       </c>
       <c r="P160" s="1" t="s">
         <v>524</v>
@@ -11850,7 +12705,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" customHeight="1" spans="1:20">
       <c r="A161" s="1" t="s">
         <v>443</v>
       </c>
@@ -11864,7 +12719,7 @@
         <v>513</v>
       </c>
       <c r="E161" s="1">
-        <v>4590.0</v>
+        <v>4590</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>37</v>
@@ -11888,7 +12743,7 @@
         <v>527</v>
       </c>
       <c r="O161" s="1">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="P161" s="1" t="s">
         <v>526</v>
@@ -11906,7 +12761,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" customHeight="1" spans="1:20">
       <c r="A162" s="1" t="s">
         <v>443</v>
       </c>
@@ -11920,7 +12775,7 @@
         <v>513</v>
       </c>
       <c r="E162" s="1">
-        <v>14723.0</v>
+        <v>14723</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>38</v>
@@ -11944,7 +12799,7 @@
         <v>531</v>
       </c>
       <c r="O162" s="1">
-        <v>928.0</v>
+        <v>928</v>
       </c>
       <c r="P162" s="1" t="s">
         <v>530</v>
@@ -11962,7 +12817,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" customHeight="1" spans="1:20">
       <c r="A163" s="1" t="s">
         <v>443</v>
       </c>
@@ -11976,7 +12831,7 @@
         <v>533</v>
       </c>
       <c r="E163" s="1">
-        <v>176509.0</v>
+        <v>176509</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>29</v>
@@ -12021,7 +12876,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" customHeight="1" spans="1:20">
       <c r="A164" s="1" t="s">
         <v>443</v>
       </c>
@@ -12035,7 +12890,7 @@
         <v>533</v>
       </c>
       <c r="E164" s="1">
-        <v>19858.0</v>
+        <v>19858</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>36</v>
@@ -12080,7 +12935,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" customHeight="1" spans="1:20">
       <c r="A165" s="1" t="s">
         <v>443</v>
       </c>
@@ -12094,7 +12949,7 @@
         <v>533</v>
       </c>
       <c r="E165" s="1">
-        <v>12247.0</v>
+        <v>12247</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>37</v>
@@ -12136,7 +12991,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" customHeight="1" spans="1:20">
       <c r="A166" s="1" t="s">
         <v>443</v>
       </c>
@@ -12150,7 +13005,7 @@
         <v>533</v>
       </c>
       <c r="E166" s="1">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>38</v>
@@ -12162,37 +13017,37 @@
         <v>32</v>
       </c>
       <c r="K166" s="1">
-        <v>724.0</v>
+        <v>724</v>
       </c>
       <c r="L166" s="1">
-        <v>682.0</v>
+        <v>682</v>
       </c>
       <c r="M166" s="1">
-        <v>724.0</v>
+        <v>724</v>
       </c>
       <c r="N166" s="1">
-        <v>564.0</v>
+        <v>564</v>
       </c>
       <c r="O166" s="1">
-        <v>215.0</v>
+        <v>215</v>
       </c>
       <c r="P166" s="1">
-        <v>682.0</v>
+        <v>682</v>
       </c>
       <c r="Q166" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R166" s="1">
-        <v>447.0</v>
+        <v>447</v>
       </c>
       <c r="S166" s="1">
-        <v>724.0</v>
+        <v>724</v>
       </c>
       <c r="T166" s="1">
-        <v>724.0</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="1:20">
       <c r="A167" s="1" t="s">
         <v>553</v>
       </c>
@@ -12206,7 +13061,7 @@
         <v>556</v>
       </c>
       <c r="E167" s="1">
-        <v>173507.0</v>
+        <v>173507</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>29</v>
@@ -12251,7 +13106,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" customHeight="1" spans="1:20">
       <c r="A168" s="1" t="s">
         <v>553</v>
       </c>
@@ -12265,7 +13120,7 @@
         <v>556</v>
       </c>
       <c r="E168" s="1">
-        <v>10815.0</v>
+        <v>10815</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>36</v>
@@ -12310,7 +13165,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" customHeight="1" spans="1:20">
       <c r="A169" s="1" t="s">
         <v>553</v>
       </c>
@@ -12324,7 +13179,7 @@
         <v>556</v>
       </c>
       <c r="E169" s="1">
-        <v>5128.0</v>
+        <v>5128</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>37</v>
@@ -12366,7 +13221,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" customHeight="1" spans="1:20">
       <c r="A170" s="1" t="s">
         <v>553</v>
       </c>
@@ -12380,7 +13235,7 @@
         <v>556</v>
       </c>
       <c r="E170" s="1">
-        <v>13824.0</v>
+        <v>13824</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>38</v>
@@ -12422,7 +13277,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" customHeight="1" spans="1:20">
       <c r="A171" s="1" t="s">
         <v>553</v>
       </c>
@@ -12436,7 +13291,7 @@
         <v>583</v>
       </c>
       <c r="E171" s="1">
-        <v>154013.0</v>
+        <v>154013</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>29</v>
@@ -12481,7 +13336,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" customHeight="1" spans="1:20">
       <c r="A172" s="1" t="s">
         <v>553</v>
       </c>
@@ -12495,7 +13350,7 @@
         <v>583</v>
       </c>
       <c r="E172" s="1">
-        <v>10454.0</v>
+        <v>10454</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>36</v>
@@ -12522,7 +13377,7 @@
         <v>597</v>
       </c>
       <c r="O172" s="1">
-        <v>591.0</v>
+        <v>591</v>
       </c>
       <c r="P172" s="1" t="s">
         <v>598</v>
@@ -12540,7 +13395,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" customHeight="1" spans="1:20">
       <c r="A173" s="1" t="s">
         <v>553</v>
       </c>
@@ -12554,7 +13409,7 @@
         <v>583</v>
       </c>
       <c r="E173" s="1">
-        <v>1787.0</v>
+        <v>1787</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>37</v>
@@ -12575,10 +13430,10 @@
         <v>599</v>
       </c>
       <c r="N173" s="1">
-        <v>428.0</v>
+        <v>428</v>
       </c>
       <c r="O173" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="P173" s="1" t="s">
         <v>600</v>
@@ -12596,7 +13451,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" customHeight="1" spans="1:20">
       <c r="A174" s="1" t="s">
         <v>553</v>
       </c>
@@ -12610,7 +13465,7 @@
         <v>583</v>
       </c>
       <c r="E174" s="1">
-        <v>12997.0</v>
+        <v>12997</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>38</v>
@@ -12634,7 +13489,7 @@
         <v>603</v>
       </c>
       <c r="O174" s="1">
-        <v>819.0</v>
+        <v>819</v>
       </c>
       <c r="P174" s="1" t="s">
         <v>602</v>
@@ -12652,7 +13507,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" customHeight="1" spans="1:20">
       <c r="A175" s="1" t="s">
         <v>553</v>
       </c>
@@ -12666,7 +13521,7 @@
         <v>605</v>
       </c>
       <c r="E175" s="1">
-        <v>277895.0</v>
+        <v>277895</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>29</v>
@@ -12711,7 +13566,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" customHeight="1" spans="1:20">
       <c r="A176" s="1" t="s">
         <v>553</v>
       </c>
@@ -12725,7 +13580,7 @@
         <v>605</v>
       </c>
       <c r="E176" s="1">
-        <v>32752.0</v>
+        <v>32752</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>36</v>
@@ -12770,7 +13625,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" customHeight="1" spans="1:20">
       <c r="A177" s="1" t="s">
         <v>553</v>
       </c>
@@ -12784,7 +13639,7 @@
         <v>605</v>
       </c>
       <c r="E177" s="1">
-        <v>15752.0</v>
+        <v>15752</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>37</v>
@@ -12808,7 +13663,7 @@
         <v>623</v>
       </c>
       <c r="O177" s="1">
-        <v>586.0</v>
+        <v>586</v>
       </c>
       <c r="P177" s="1" t="s">
         <v>622</v>
@@ -12826,7 +13681,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" customHeight="1" spans="1:20">
       <c r="A178" s="1" t="s">
         <v>553</v>
       </c>
@@ -12840,7 +13695,7 @@
         <v>605</v>
       </c>
       <c r="E178" s="1">
-        <v>42603.0</v>
+        <v>42603</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>38</v>
@@ -12882,7 +13737,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" customHeight="1" spans="1:20">
       <c r="A179" s="1" t="s">
         <v>630</v>
       </c>
@@ -12896,7 +13751,7 @@
         <v>633</v>
       </c>
       <c r="E179" s="1">
-        <v>12856.0</v>
+        <v>12856</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>29</v>
@@ -12923,7 +13778,7 @@
         <v>639</v>
       </c>
       <c r="O179" s="1">
-        <v>692.0</v>
+        <v>692</v>
       </c>
       <c r="P179" s="1" t="s">
         <v>640</v>
@@ -12941,7 +13796,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" customHeight="1" spans="1:20">
       <c r="A180" s="1" t="s">
         <v>630</v>
       </c>
@@ -12955,7 +13810,7 @@
         <v>633</v>
       </c>
       <c r="E180" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>36</v>
@@ -12997,7 +13852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" customHeight="1" spans="1:20">
       <c r="A181" s="1" t="s">
         <v>630</v>
       </c>
@@ -13011,7 +13866,7 @@
         <v>633</v>
       </c>
       <c r="E181" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>37</v>
@@ -13053,7 +13908,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" customHeight="1" spans="1:20">
       <c r="A182" s="1" t="s">
         <v>630</v>
       </c>
@@ -13067,7 +13922,7 @@
         <v>633</v>
       </c>
       <c r="E182" s="1">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>38</v>
@@ -13079,37 +13934,37 @@
         <v>32</v>
       </c>
       <c r="K182" s="1">
-        <v>174.0</v>
+        <v>174</v>
       </c>
       <c r="L182" s="1">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="M182" s="1">
-        <v>174.0</v>
+        <v>174</v>
       </c>
       <c r="N182" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="O182" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="P182" s="1">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="Q182" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R182" s="1">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="S182" s="1">
-        <v>174.0</v>
+        <v>174</v>
       </c>
       <c r="T182" s="1">
-        <v>174.0</v>
-      </c>
-    </row>
-    <row r="183">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:20">
       <c r="A183" s="1" t="s">
         <v>630</v>
       </c>
@@ -13123,7 +13978,7 @@
         <v>642</v>
       </c>
       <c r="E183" s="1">
-        <v>39460.0</v>
+        <v>39460</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>29</v>
@@ -13168,7 +14023,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" customHeight="1" spans="1:20">
       <c r="A184" s="1" t="s">
         <v>630</v>
       </c>
@@ -13182,7 +14037,7 @@
         <v>642</v>
       </c>
       <c r="E184" s="1">
-        <v>1457.0</v>
+        <v>1457</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>36</v>
@@ -13209,7 +14064,7 @@
         <v>32</v>
       </c>
       <c r="O184" s="1">
-        <v>546.0</v>
+        <v>546</v>
       </c>
       <c r="P184" s="1" t="s">
         <v>653</v>
@@ -13227,7 +14082,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" customHeight="1" spans="1:20">
       <c r="A185" s="1" t="s">
         <v>630</v>
       </c>
@@ -13241,7 +14096,7 @@
         <v>642</v>
       </c>
       <c r="E185" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>37</v>
@@ -13253,22 +14108,22 @@
         <v>32</v>
       </c>
       <c r="K185" s="1">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="L185" s="1">
-        <v>583.0</v>
+        <v>583</v>
       </c>
       <c r="M185" s="1">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="N185" s="1">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="O185" s="1">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="P185" s="1">
-        <v>583.0</v>
+        <v>583</v>
       </c>
       <c r="Q185" s="1" t="s">
         <v>32</v>
@@ -13277,13 +14132,13 @@
         <v>32</v>
       </c>
       <c r="S185" s="1">
-        <v>620.0</v>
+        <v>620</v>
       </c>
       <c r="T185" s="1">
-        <v>620.0</v>
-      </c>
-    </row>
-    <row r="186">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:20">
       <c r="A186" s="1" t="s">
         <v>630</v>
       </c>
@@ -13297,7 +14152,7 @@
         <v>642</v>
       </c>
       <c r="E186" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>38</v>
@@ -13339,7 +14194,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" customHeight="1" spans="1:20">
       <c r="A187" s="1" t="s">
         <v>630</v>
       </c>
@@ -13353,7 +14208,7 @@
         <v>655</v>
       </c>
       <c r="E187" s="1">
-        <v>15847.0</v>
+        <v>15847</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>29</v>
@@ -13380,7 +14235,7 @@
         <v>662</v>
       </c>
       <c r="O187" s="1">
-        <v>852.0</v>
+        <v>852</v>
       </c>
       <c r="P187" s="1" t="s">
         <v>663</v>
@@ -13398,7 +14253,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" customHeight="1" spans="1:20">
       <c r="A188" s="1" t="s">
         <v>630</v>
       </c>
@@ -13412,7 +14267,7 @@
         <v>655</v>
       </c>
       <c r="E188" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>36</v>
@@ -13454,7 +14309,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" customHeight="1" spans="1:20">
       <c r="A189" s="1" t="s">
         <v>630</v>
       </c>
@@ -13468,7 +14323,7 @@
         <v>655</v>
       </c>
       <c r="E189" s="1">
-        <v>1324.0</v>
+        <v>1324</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>37</v>
@@ -13489,10 +14344,10 @@
         <v>665</v>
       </c>
       <c r="N189" s="1">
-        <v>395.0</v>
+        <v>395</v>
       </c>
       <c r="O189" s="1">
-        <v>159.0</v>
+        <v>159</v>
       </c>
       <c r="P189" s="1" t="s">
         <v>666</v>
@@ -13501,7 +14356,7 @@
         <v>32</v>
       </c>
       <c r="R189" s="1">
-        <v>794.0</v>
+        <v>794</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>665</v>
@@ -13510,7 +14365,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" customHeight="1" spans="1:20">
       <c r="A190" s="1" t="s">
         <v>630</v>
       </c>
@@ -13524,7 +14379,7 @@
         <v>655</v>
       </c>
       <c r="E190" s="1">
-        <v>3071.0</v>
+        <v>3071</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>38</v>
@@ -13545,7 +14400,7 @@
         <v>667</v>
       </c>
       <c r="N190" s="1">
-        <v>917.0</v>
+        <v>917</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>669</v>
@@ -13566,7 +14421,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" customHeight="1" spans="1:20">
       <c r="A191" s="1" t="s">
         <v>630</v>
       </c>
@@ -13580,7 +14435,7 @@
         <v>672</v>
       </c>
       <c r="E191" s="1">
-        <v>10178.0</v>
+        <v>10178</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>29</v>
@@ -13607,7 +14462,7 @@
         <v>679</v>
       </c>
       <c r="O191" s="1">
-        <v>547.0</v>
+        <v>547</v>
       </c>
       <c r="P191" s="1" t="s">
         <v>677</v>
@@ -13625,7 +14480,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" customHeight="1" spans="1:20">
       <c r="A192" s="1" t="s">
         <v>630</v>
       </c>
@@ -13639,7 +14494,7 @@
         <v>672</v>
       </c>
       <c r="E192" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>36</v>
@@ -13681,7 +14536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" customHeight="1" spans="1:20">
       <c r="A193" s="1" t="s">
         <v>630</v>
       </c>
@@ -13695,7 +14550,7 @@
         <v>672</v>
       </c>
       <c r="E193" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>37</v>
@@ -13737,7 +14592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" customHeight="1" spans="1:20">
       <c r="A194" s="1" t="s">
         <v>630</v>
       </c>
@@ -13751,7 +14606,7 @@
         <v>672</v>
       </c>
       <c r="E194" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>38</v>
@@ -13793,7 +14648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" customHeight="1" spans="1:20">
       <c r="A195" s="1" t="s">
         <v>680</v>
       </c>
@@ -13807,7 +14662,7 @@
         <v>682</v>
       </c>
       <c r="E195" s="1">
-        <v>33075.0</v>
+        <v>33075</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>29</v>
@@ -13828,7 +14683,7 @@
         <v>686</v>
       </c>
       <c r="M195" s="1">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="N195" s="1" t="s">
         <v>687</v>
@@ -13852,7 +14707,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" customHeight="1" spans="1:20">
       <c r="A196" s="1" t="s">
         <v>680</v>
       </c>
@@ -13866,7 +14721,7 @@
         <v>682</v>
       </c>
       <c r="E196" s="1">
-        <v>6615.0</v>
+        <v>6615</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>36</v>
@@ -13893,7 +14748,7 @@
         <v>692</v>
       </c>
       <c r="O196" s="1">
-        <v>359.0</v>
+        <v>359</v>
       </c>
       <c r="P196" s="1" t="s">
         <v>691</v>
@@ -13911,7 +14766,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" customHeight="1" spans="1:20">
       <c r="A197" s="1" t="s">
         <v>680</v>
       </c>
@@ -13925,7 +14780,7 @@
         <v>682</v>
       </c>
       <c r="E197" s="1">
-        <v>672.0</v>
+        <v>672</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>37</v>
@@ -13937,22 +14792,22 @@
         <v>32</v>
       </c>
       <c r="K197" s="1">
-        <v>571.0</v>
+        <v>571</v>
       </c>
       <c r="L197" s="1">
-        <v>538.0</v>
+        <v>538</v>
       </c>
       <c r="M197" s="1">
-        <v>571.0</v>
+        <v>571</v>
       </c>
       <c r="N197" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="O197" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="P197" s="1">
-        <v>538.0</v>
+        <v>538</v>
       </c>
       <c r="Q197" s="1" t="s">
         <v>32</v>
@@ -13961,13 +14816,13 @@
         <v>32</v>
       </c>
       <c r="S197" s="1">
-        <v>571.0</v>
+        <v>571</v>
       </c>
       <c r="T197" s="1">
-        <v>571.0</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="1:20">
       <c r="A198" s="1" t="s">
         <v>680</v>
       </c>
@@ -13981,7 +14836,7 @@
         <v>682</v>
       </c>
       <c r="E198" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>38</v>
@@ -14023,7 +14878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" customHeight="1" spans="1:20">
       <c r="A199" s="1" t="s">
         <v>693</v>
       </c>
@@ -14037,7 +14892,7 @@
         <v>695</v>
       </c>
       <c r="E199" s="1">
-        <v>73317.0</v>
+        <v>73317</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>36</v>
@@ -14082,7 +14937,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" customHeight="1" spans="1:20">
       <c r="A200" s="1" t="s">
         <v>693</v>
       </c>
@@ -14096,7 +14951,7 @@
         <v>695</v>
       </c>
       <c r="E200" s="1">
-        <v>45690.0</v>
+        <v>45690</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>29</v>
@@ -14141,7 +14996,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" customHeight="1" spans="1:20">
       <c r="A201" s="1" t="s">
         <v>693</v>
       </c>
@@ -14155,7 +15010,7 @@
         <v>695</v>
       </c>
       <c r="E201" s="1">
-        <v>15967.0</v>
+        <v>15967</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>37</v>
@@ -14197,7 +15052,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" customHeight="1" spans="1:20">
       <c r="A202" s="1" t="s">
         <v>693</v>
       </c>
@@ -14211,7 +15066,7 @@
         <v>695</v>
       </c>
       <c r="E202" s="1">
-        <v>1588.0</v>
+        <v>1588</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>38</v>
@@ -14232,10 +15087,10 @@
         <v>715</v>
       </c>
       <c r="N202" s="1">
-        <v>370.0</v>
+        <v>370</v>
       </c>
       <c r="O202" s="1">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="P202" s="1" t="s">
         <v>716</v>
@@ -14253,7 +15108,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" customHeight="1" spans="1:20">
       <c r="A203" s="1" t="s">
         <v>693</v>
       </c>
@@ -14267,7 +15122,7 @@
         <v>719</v>
       </c>
       <c r="E203" s="1">
-        <v>107434.0</v>
+        <v>107434</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>29</v>
@@ -14309,7 +15164,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" customHeight="1" spans="1:20">
       <c r="A204" s="1" t="s">
         <v>693</v>
       </c>
@@ -14323,7 +15178,7 @@
         <v>719</v>
       </c>
       <c r="E204" s="1">
-        <v>797.0</v>
+        <v>797</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>36</v>
@@ -14335,37 +15190,37 @@
         <v>32</v>
       </c>
       <c r="K204" s="1">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="L204" s="1">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="M204" s="1">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="N204" s="1">
-        <v>524.0</v>
+        <v>524</v>
       </c>
       <c r="O204" s="1">
-        <v>271.0</v>
+        <v>271</v>
       </c>
       <c r="P204" s="1">
-        <v>638.0</v>
+        <v>638</v>
       </c>
       <c r="Q204" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R204" s="1">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="S204" s="1">
-        <v>677.0</v>
+        <v>677</v>
       </c>
       <c r="T204" s="1">
-        <v>677.0</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:20">
       <c r="A205" s="1" t="s">
         <v>693</v>
       </c>
@@ -14379,7 +15234,7 @@
         <v>719</v>
       </c>
       <c r="E205" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>37</v>
@@ -14421,7 +15276,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" customHeight="1" spans="1:20">
       <c r="A206" s="1" t="s">
         <v>693</v>
       </c>
@@ -14435,7 +15290,7 @@
         <v>719</v>
       </c>
       <c r="E206" s="1">
-        <v>695.0</v>
+        <v>695</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>38</v>
@@ -14447,37 +15302,37 @@
         <v>32</v>
       </c>
       <c r="K206" s="1">
-        <v>591.0</v>
+        <v>591</v>
       </c>
       <c r="L206" s="1">
-        <v>556.0</v>
+        <v>556</v>
       </c>
       <c r="M206" s="1">
-        <v>591.0</v>
+        <v>591</v>
       </c>
       <c r="N206" s="1">
-        <v>355.0</v>
+        <v>355</v>
       </c>
       <c r="O206" s="1">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="P206" s="1">
-        <v>556.0</v>
+        <v>556</v>
       </c>
       <c r="Q206" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R206" s="1">
-        <v>494.0</v>
+        <v>494</v>
       </c>
       <c r="S206" s="1">
-        <v>591.0</v>
+        <v>591</v>
       </c>
       <c r="T206" s="1">
-        <v>591.0</v>
-      </c>
-    </row>
-    <row r="207">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="1:20">
       <c r="A207" s="1" t="s">
         <v>693</v>
       </c>
@@ -14491,7 +15346,7 @@
         <v>727</v>
       </c>
       <c r="E207" s="1">
-        <v>31899.0</v>
+        <v>31899</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>29</v>
@@ -14533,7 +15388,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" customHeight="1" spans="1:20">
       <c r="A208" s="1" t="s">
         <v>693</v>
       </c>
@@ -14547,7 +15402,7 @@
         <v>727</v>
       </c>
       <c r="E208" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>36</v>
@@ -14559,37 +15414,37 @@
         <v>32</v>
       </c>
       <c r="K208" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="L208" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="M208" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="N208" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="O208" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="P208" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="Q208" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R208" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="S208" s="1">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="T208" s="1">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:20">
       <c r="A209" s="1" t="s">
         <v>693</v>
       </c>
@@ -14603,7 +15458,7 @@
         <v>727</v>
       </c>
       <c r="E209" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>37</v>
@@ -14645,7 +15500,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" customHeight="1" spans="1:20">
       <c r="A210" s="1" t="s">
         <v>693</v>
       </c>
@@ -14659,7 +15514,7 @@
         <v>727</v>
       </c>
       <c r="E210" s="1">
-        <v>821.0</v>
+        <v>821</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>38</v>
@@ -14671,37 +15526,37 @@
         <v>32</v>
       </c>
       <c r="K210" s="1">
-        <v>698.0</v>
+        <v>698</v>
       </c>
       <c r="L210" s="1">
-        <v>657.0</v>
+        <v>657</v>
       </c>
       <c r="M210" s="1">
-        <v>698.0</v>
+        <v>698</v>
       </c>
       <c r="N210" s="1">
-        <v>404.0</v>
+        <v>404</v>
       </c>
       <c r="O210" s="1">
-        <v>310.0</v>
+        <v>310</v>
       </c>
       <c r="P210" s="1">
-        <v>657.0</v>
+        <v>657</v>
       </c>
       <c r="Q210" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R210" s="1">
-        <v>431.0</v>
+        <v>431</v>
       </c>
       <c r="S210" s="1">
-        <v>698.0</v>
+        <v>698</v>
       </c>
       <c r="T210" s="1">
-        <v>698.0</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="1:20">
       <c r="A211" s="1" t="s">
         <v>693</v>
       </c>
@@ -14715,7 +15570,7 @@
         <v>735</v>
       </c>
       <c r="E211" s="1">
-        <v>47220.0</v>
+        <v>47220</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>29</v>
@@ -14757,7 +15612,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" customHeight="1" spans="1:20">
       <c r="A212" s="1" t="s">
         <v>693</v>
       </c>
@@ -14771,7 +15626,7 @@
         <v>735</v>
       </c>
       <c r="E212" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>36</v>
@@ -14783,37 +15638,37 @@
         <v>32</v>
       </c>
       <c r="K212" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="L212" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="M212" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="N212" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O212" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="P212" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="Q212" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R212" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="S212" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="T212" s="1">
-        <v>27.0</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="1:20">
       <c r="A213" s="1" t="s">
         <v>693</v>
       </c>
@@ -14827,7 +15682,7 @@
         <v>735</v>
       </c>
       <c r="E213" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>37</v>
@@ -14869,7 +15724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" customHeight="1" spans="1:20">
       <c r="A214" s="1" t="s">
         <v>693</v>
       </c>
@@ -14883,7 +15738,7 @@
         <v>735</v>
       </c>
       <c r="E214" s="1">
-        <v>2869.0</v>
+        <v>2869</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>38</v>
@@ -14907,7 +15762,7 @@
         <v>744</v>
       </c>
       <c r="O214" s="1">
-        <v>723.0</v>
+        <v>723</v>
       </c>
       <c r="P214" s="1" t="s">
         <v>743</v>
@@ -14925,28 +15780,19 @@
         <v>742</v>
       </c>
     </row>
-    <row r="225">
-      <c r="J225" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="K225" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="J226" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="K226" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="J227" s="1">
-        <v>0.0</v>
-      </c>
+    <row r="225" customHeight="1" spans="10:11">
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+    </row>
+    <row r="226" customHeight="1" spans="10:11">
+      <c r="J226" s="1"/>
+      <c r="K226" s="1"/>
+    </row>
+    <row r="227" customHeight="1" spans="10:11">
+      <c r="J227" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>